--- a/olympic_simulator/media/simulacion_Copa Sudamericana_1880.xlsx
+++ b/olympic_simulator/media/simulacion_Copa Sudamericana_1880.xlsx
@@ -489,29 +489,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -520,29 +520,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -551,29 +551,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>SC Corinthians</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -598,13 +598,13 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="9">
@@ -639,217 +639,217 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SC Corinthians</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SC Corinthians</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SC Corinthians</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SC Corinthians</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SC Corinthians</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SC Corinthians</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -926,29 +926,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -957,29 +957,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -988,29 +988,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -1019,29 +1019,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1094,16 +1094,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1112,29 +1112,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1143,29 +1143,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="11">
@@ -1174,29 +1174,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1205,29 +1205,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1249,16 +1249,16 @@
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ceara SC</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1298,26 +1298,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1345,13 +1345,13 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="17">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1373,16 +1373,16 @@
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1407,10 +1407,10 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1422,29 +1422,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
@@ -1453,29 +1453,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC Corinthians</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1484,29 +1484,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens FC</t>
+          <t>Club Cerro Portenio</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="22">
@@ -1515,29 +1515,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>CA Rosario Central</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
@@ -1546,26 +1546,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CA Boston River</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
         <v>-5</v>
@@ -1577,29 +1577,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CD Real Sociedad</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
@@ -1608,26 +1608,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Club Universitario de Deportes</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
         <v>-3</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportivo Rayo Zuliano</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1655,10 +1655,10 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
         <v>-4</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CA Rosario Central</t>
+          <t>SC Corinthians</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1686,13 +1686,13 @@
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I27" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="28">
@@ -1701,29 +1701,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anzoategui FC</t>
+          <t>Academia Puerto Cabello</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="29">
@@ -1732,29 +1732,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CD Union la Calera</t>
+          <t>CA Progreso</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="30">
@@ -1763,29 +1763,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FC Universitario de Vinto</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I30" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="31">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CA Newells Old Boys</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1813,10 +1813,10 @@
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="32">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1841,13 +1841,13 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I32" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="33">
@@ -1856,29 +1856,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CA Banfield</t>
+          <t>GV CD San Jose</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="34">
@@ -1887,29 +1887,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>CD San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>5</v>
       </c>
       <c r="H34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="37">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>7</v>
       </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2050,22 +2050,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -2077,29 +2077,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Deportivo Rayo Zuliano</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CA Banfield</t>
+          <t>CD San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2124,10 +2124,10 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
         <v>-4</v>
@@ -2165,70 +2165,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA Banfield</t>
+          <t>Deportivo Rayo Zuliano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ceara SC</t>
+          <t>CD San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ceara SC</t>
+          <t>CD San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CA Banfield</t>
+          <t>Deportivo Rayo Zuliano</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2237,106 +2237,106 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CA Banfield</t>
+          <t>Deportivo Rayo Zuliano</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CD San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Ceara SC</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CF Monterrey</t>
-        </is>
-      </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ceara SC</t>
+          <t>CD San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Banfield</t>
+          <t>Deportivo Rayo Zuliano</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ceara SC</t>
+          <t>CD San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CA Banfield</t>
+          <t>Deportivo Rayo Zuliano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
@@ -2345,34 +2345,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CA Banfield</t>
+          <t>Deportivo Rayo Zuliano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ceara SC</t>
+          <t>CD San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2452,29 +2452,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2483,29 +2483,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2514,29 +2514,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CD Union la Calera</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
         <v>8</v>
       </c>
-      <c r="H5" t="n">
-        <v>14</v>
-      </c>
       <c r="I5" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2545,29 +2545,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Universitario de Vinto</t>
+          <t>CA Progreso</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9">
@@ -2602,210 +2602,210 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FC Universitario de Vinto</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CD Union la Calera</t>
+          <t>CA Progreso</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FC Universitario de Vinto</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CD Union la Calera</t>
+          <t>CA Progreso</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FC Universitario de Vinto</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CD Union la Calera</t>
+          <t>CA Progreso</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FC Universitario de Vinto</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CD Union la Calera</t>
+          <t>CA Progreso</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CD Union la Calera</t>
+          <t>CA Progreso</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FC Universitario de Vinto</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FC Universitario de Vinto</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CD Union la Calera</t>
+          <t>CA Progreso</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2908,10 +2908,10 @@
         <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2920,29 +2920,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2951,29 +2951,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CA Rosario Central</t>
+          <t>Academia Puerto Cabello</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>GV CD San Jose</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3001,10 +3001,10 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="9">
@@ -3039,12 +3039,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3057,106 +3057,106 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>GV CD San Jose</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CA Rosario Central</t>
+          <t>Academia Puerto Cabello</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CA Rosario Central</t>
+          <t>Academia Puerto Cabello</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>GV CD San Jose</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>GV CD San Jose</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CA Rosario Central</t>
+          <t>Academia Puerto Cabello</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
@@ -3165,16 +3165,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CA Rosario Central</t>
+          <t>Academia Puerto Cabello</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>GV CD San Jose</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -3183,52 +3183,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CA Rosario Central</t>
+          <t>Academia Puerto Cabello</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>GV CD San Jose</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>GV CD San Jose</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -3237,16 +3237,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CA Rosario Central</t>
+          <t>Academia Puerto Cabello</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -3326,29 +3326,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -3357,29 +3357,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3388,29 +3388,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CD Real Sociedad</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3419,29 +3419,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anzoategui FC</t>
+          <t>CA Rosario Central</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
@@ -3476,34 +3476,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CD Real Sociedad</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>CA Rosario Central</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anzoategui FC</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -3512,34 +3512,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CD Real Sociedad</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anzoategui FC</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>CA Rosario Central</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -3548,52 +3548,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CD Real Sociedad</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>CA Rosario Central</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anzoategui FC</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CD Real Sociedad</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3602,91 +3602,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Anzoategui FC</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>CA Rosario Central</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Anzoategui FC</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CD Real Sociedad</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>CA Rosario Central</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>CA Rosario Central</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CD Real Sociedad</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Anzoategui FC</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3763,29 +3763,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3810,10 +3810,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
         <v>7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -3825,29 +3825,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>CA Boston River</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="6">
@@ -3856,29 +3856,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="H6" t="n">
-        <v>12</v>
-      </c>
       <c r="I6" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="9">
@@ -3913,48 +3913,48 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>CA Boston River</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>CA Boston River</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3967,34 +3967,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -4003,127 +4003,127 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>CA Boston River</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>CA Boston River</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>CA Boston River</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>CA Boston River</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4200,29 +4200,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4231,29 +4231,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -4262,26 +4262,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>Club Cerro Portenio</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
         <v>-2</v>
@@ -4293,29 +4293,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CA Newells Old Boys</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="9">
@@ -4350,52 +4350,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>CA Newells Old Boys</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Club Cerro Portenio</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Club Cerro Portenio</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -4404,163 +4404,163 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>CA Newells Old Boys</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Club Cerro Portenio</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>CA Newells Old Boys</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>CA Newells Old Boys</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Club Cerro Portenio</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Club Cerro Portenio</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>CA Newells Old Boys</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>CA Newells Old Boys</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Club Cerro Portenio</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4637,29 +4637,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -4668,29 +4668,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4699,29 +4699,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SC Corinthians</t>
+          <t>Club Universitario de Deportes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="6">
@@ -4730,29 +4730,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens FC</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="9">
@@ -4787,88 +4787,88 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>Club Universitario de Deportes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SC Corinthians</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tivoli Gardens FC</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>Club Universitario de Deportes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tivoli Gardens FC</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SC Corinthians</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>Club Universitario de Deportes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -4877,16 +4877,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens FC</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC Corinthians</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -4895,109 +4895,109 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SC Corinthians</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>Club Universitario de Deportes</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens FC</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens FC</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>Club Universitario de Deportes</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC Corinthians</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>Club Universitario de Deportes</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SC Corinthians</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tivoli Gardens FC</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5090,13 +5090,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5121,13 +5121,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5136,29 +5136,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5167,29 +5167,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="7">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5214,13 +5214,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5307,10 +5307,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5335,16 +5335,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5353,29 +5353,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5384,26 +5384,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>-1</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5431,10 +5431,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>-1</v>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ceara SC</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5462,13 +5462,13 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5496,10 +5496,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5527,10 +5527,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5558,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="21">
@@ -5596,52 +5596,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ceara SC</t>
+          <t>CD Universidad Catolica de Chile</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SC Internacional</t>
+          <t>CSD Colo Colo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -5650,102 +5650,102 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Club Sport Huancayo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF Cruz Azul</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deportivo Binacional FC</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Liga de Quito</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CD Garcilaso</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CA Tembetary</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>SC Recife</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -5758,88 +5758,88 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>CD Lobos UPNFM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CA Boston River</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GV CD San Jose</t>
+          <t>CA Banfield</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
@@ -5848,37 +5848,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Club Atletico Mineiro</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Club Libertad</t>
+          <t>Ceara SC</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CF Monterrey</t>
+          <t>Portmore United FC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA San Lorenzo de Almagro</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
